--- a/daily_matches/job_matches_2026-08-19.xlsx
+++ b/daily_matches/job_matches_2026-08-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>IT Data Engineer IV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nexstar Media Group, Inc.</t>
+          <t>SouthState Bank</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Winter Haven, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, S3, EC2</t>
+          <t>RAG, Redshift, BigQuery, Synapse, Docker, Kubernetes, CI/CD, Snowflake, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5960a42e79ce1d</t>
+          <t>https://www.indeed.com/viewjob?jk=89c590723bea472d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior UI Engineer (React/React Native &amp; AI Development) - Plano, TX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Git, Snowflake, PostgreSQL, Tableau</t>
+          <t>LangChain, RAG, Gemini, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5bcc00949b0b05a</t>
+          <t>https://www.indeed.com/viewjob?jk=be70c680c70ebca2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Git, Snowflake, PostgreSQL, Tableau</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, Git, Databricks, Hadoop, NoSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f9d967bd29018a</t>
+          <t>https://www.indeed.com/viewjob?jk=30414b2a85fbe095</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Simulation &amp; ML Platform</t>
+          <t>App Dev &amp; Support Services Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intuitive (Intuitive Surgical)</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Somerset, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Kafka, Python, R</t>
+          <t>Generative AI, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4079b75f735c8f09</t>
+          <t>https://www.indeed.com/viewjob?jk=331526dcce8bdbb4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Artificial Intelligence Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Hugging Face, TensorFlow, PyTorch, Keras, Git, R, Optimization</t>
+          <t>RAG, Redshift, Apache Airflow, CI/CD, Jenkins, Git, Redshift, PostgreSQL, Tableau, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca0054bdd293eb16</t>
+          <t>https://www.indeed.com/viewjob?jk=ddee801b38d94382</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Dataflow, CI/CD, Git, PySpark, Power BI, Python, SQL, R</t>
+          <t>RAG, Kinesis, CI/CD, Jenkins, Git, Kafka, PostgreSQL, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230993df38e10727</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a4f8b2a53df275</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer, CX Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+          <t>RAG, Kinesis, CI/CD, Jenkins, Git, Kafka, PostgreSQL, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9762aedfb61c04</t>
+          <t>https://www.indeed.com/viewjob?jk=71e4ae5e09b571ae</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>CDP Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Azure ML, Python, R, Optimization, Bayesian</t>
+          <t>Data Scientist, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e530aed96727d232</t>
+          <t>https://www.indeed.com/viewjob?jk=8550b60dfa07a9a8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>2027 Data &amp; AI Program - Summer Internship - Analyst - United States</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Azure ML, Python, R, Optimization, Bayesian</t>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=525e767c837605b5</t>
+          <t>https://www.indeed.com/viewjob?jk=411d31a6d1a79340</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>bareinsights</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Azure ML, Python, R, Optimization, Bayesian</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d784203bf60c397</t>
+          <t>https://www.indeed.com/viewjob?jk=f99653e875f1b81d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Solutions Engineer, DevOps - Central</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Prompt Engineering, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Data Lake, CI/CD, Jenkins, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90940301e4c43216</t>
+          <t>https://www.indeed.com/viewjob?jk=96b3c17f710c4b52</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Database Administration Managed Services Engineer III</t>
+          <t>QA Validation Engineer for AI Initiatives</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, PostgreSQL, Python, SQL, R, Optimization</t>
+          <t>Generative AI, Prompt Engineering, Data Lake, CI/CD, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,42 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1122ee28ffddd2</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1a4313ef8c3f8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist / Analyst, Finance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Polymarket</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5328002055ae982</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-19.xlsx
+++ b/daily_matches/job_matches_2026-08-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IT Data Engineer IV</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SouthState Bank</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Winter Haven, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Synapse, Docker, Kubernetes, CI/CD, Snowflake, BigQuery, Redshift</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Azure ML, MLflow, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c590723bea472d</t>
+          <t>https://www.indeed.com/viewjob?jk=1864e32484d3961d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior UI Engineer (React/React Native &amp; AI Development) - Plano, TX</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Rearc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Gemini, Copilot, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Python</t>
+          <t>AI Engineer, RAG, MLflow, FastAPI, Docker, CI/CD, Databricks, PostgreSQL, MySQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be70c680c70ebca2</t>
+          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Data Scientist Associate-AI Solutions</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>UnityPoint Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, Git, Databricks, Hadoop, NoSQL, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30414b2a85fbe095</t>
+          <t>https://www.indeed.com/viewjob?jk=222d8e8e7fd9593c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Services Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Somerset, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL</t>
+          <t>RAG, Pinecone, Glue, Synapse, CI/CD, Git, Databricks, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=331526dcce8bdbb4</t>
+          <t>https://www.indeed.com/viewjob?jk=2548708b2a40faf0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Apache Airflow, CI/CD, Jenkins, Git, Redshift, PostgreSQL, Tableau, Python</t>
+          <t>RAG, Pinecone, Glue, Synapse, CI/CD, Git, Databricks, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddee801b38d94382</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d7679f31c13e80</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, CI/CD, Jenkins, Git, Kafka, PostgreSQL, NoSQL, SQL, R</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a4f8b2a53df275</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcc3836acd1acef</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Precor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, CI/CD, Jenkins, Git, Kafka, PostgreSQL, NoSQL, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, BigQuery, Dataflow, BigQuery, Power BI, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e4ae5e09b571ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b4034e6e04fe0f86</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CDP Data Engineer</t>
+          <t>Senior Oracle HCM Automation +AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Nvizion solutions pvt. ltd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Git, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8550b60dfa07a9a8</t>
+          <t>https://www.indeed.com/viewjob?jk=84d8f084b0d90f4a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2027 Data &amp; AI Program - Summer Internship - Analyst - United States</t>
+          <t>Data &amp; Analytics Enterprise Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Principal Financial Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Data Lake, Snowflake, Databricks, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,147 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=411d31a6d1a79340</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>bareinsights</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f99653e875f1b81d</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Database Administrator</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Index Analytics LLC</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, CI/CD, Jenkins, Git, Snowflake, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96b3c17f710c4b52</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>QA Validation Engineer for AI Initiatives</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Teradyne</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>North Reading, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Generative AI, Prompt Engineering, Data Lake, CI/CD, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1a4313ef8c3f8f</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist / Analyst, Finance</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Polymarket</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d5328002055ae982</t>
+          <t>https://www.indeed.com/viewjob?jk=f20aa9c2229f0ea5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-19.xlsx
+++ b/daily_matches/job_matches_2026-08-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior AI/ML Engineer Remote — Full Time Remote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,34 +486,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Azure ML, MLflow, Docker</t>
+          <t>RAG, TensorFlow, PyTorch, XGBoost, S3, Kinesis, FastAPI, Docker, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1864e32484d3961d</t>
+          <t>https://www.indeed.com/viewjob?jk=76c5165dd6d5386f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rearc</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, MLflow, FastAPI, Docker, CI/CD, Databricks, PostgreSQL, MySQL, Python</t>
+          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dae65756fc60c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1637275a51361381</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist Associate-AI Solutions</t>
+          <t>(New College Graduate) Associate AI &amp; Data Engineering Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UnityPoint Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Databricks, Python</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222d8e8e7fd9593c</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0a4bbd7b800b4c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, Glue, Synapse, CI/CD, Git, Databricks, PostgreSQL, MongoDB, NoSQL</t>
+          <t>RAG, Synapse, Data Lake, AKS, CI/CD, Terraform, Git, Databricks, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2548708b2a40faf0</t>
+          <t>https://www.indeed.com/viewjob?jk=bb26bb0ae7057381</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>WM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, Glue, Synapse, CI/CD, Git, Databricks, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Data Scientist, S3, EC2, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d7679f31c13e80</t>
+          <t>https://www.indeed.com/viewjob?jk=389fc2ed5c0deb4b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, GitHub Actions, Git, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcc3836acd1acef</t>
+          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Precor</t>
+          <t>AiroDigital LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, BigQuery, Dataflow, BigQuery, Power BI, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4034e6e04fe0f86</t>
+          <t>https://www.indeed.com/viewjob?jk=019c0aea03ae8a58</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Oracle HCM Automation +AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nvizion solutions pvt. ltd</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Git, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, AKS, Hadoop, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84d8f084b0d90f4a</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Data &amp; Analytics Enterprise Architect</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Principal Financial Group</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Data Lake, Snowflake, Databricks, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f20aa9c2229f0ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5ebf48050b98fc</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-19.xlsx
+++ b/daily_matches/job_matches_2026-08-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer Remote — Full Time Remote</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, XGBoost, S3, Kinesis, FastAPI, Docker, GitHub Actions, Git</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c5165dd6d5386f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0cc997ffaad767</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1637275a51361381</t>
+          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>(New College Graduate) Associate AI &amp; Data Engineering Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, NoSQL, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0a4bbd7b800b4c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ETS Senior Engineer - Azure Databricks &amp; Data Platform Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, AKS, CI/CD, Terraform, Git, Databricks, PostgreSQL, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb26bb0ae7057381</t>
+          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WM</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389fc2ed5c0deb4b</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, GitHub Actions, Git, Kafka, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221814563679cbed</t>
+          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AiroDigital LLC</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,427 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019c0aea03ae8a58</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca6afc769938392</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, S3, Glue, Redshift, CI/CD, Git, Snowflake, Databricks, Redshift, Python</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Proscia</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, SQL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Automation Tester</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c78af16e0a852a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (L5)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Exiger</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42c03602c2583f2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (L5)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Exiger</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd96deb9d86f0b77</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Jefferson Center for Mental Health</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Wheat Ridge, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Software Engineer, Inference (AI Data Engineering)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SpaceX</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=666f2ebd7f91f325</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Zoom Communications</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, CI/CD, Git, Snowflake, Databricks, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Motorola Solutions</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d4bfa59e40a5e45</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Claude AI Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, AKS, Hadoop, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac5ebf48050b98fc</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1295b90fb790979e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Kubernetes Platform Administrator</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MKS2 Technologies</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7acfe2de3765c880</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI Engineer/Banking Domain</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, Hugging Face, TensorFlow, PyTorch, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8389d2351331bb64</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-19.xlsx
+++ b/daily_matches/job_matches_2026-08-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>Generative AI, RAG, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0cc997ffaad767</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed75a25bf648004</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Oteemo, Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake</t>
+          <t>Generative AI, RAG, Gemini, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f0df91f1d27621</t>
+          <t>https://www.indeed.com/viewjob?jk=7510a53669a6bd9e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>ICONICS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake</t>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb2afafd3cbfe7a</t>
+          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Matoffo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2236d5961d42b1a6</t>
+          <t>https://www.indeed.com/viewjob?jk=9135a734bc453bc3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake</t>
+          <t>RAG, Redshift, Kinesis, CI/CD, Terraform, Git, Snowflake, Databricks, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6120725df09583</t>
+          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Generative AI Engineer / QA Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, CI/CD, Snowflake, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdbca9d10a3e1257</t>
+          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer II - Java, AI - ​Amex Offers &amp; Digital Media</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca6afc769938392</t>
+          <t>https://www.indeed.com/viewjob?jk=a69ff9ff69aac8b3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Redshift, CI/CD, Git, Snowflake, Databricks, Redshift, Python</t>
+          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, BigQuery, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964835924f3b368c</t>
+          <t>https://www.indeed.com/viewjob?jk=4134fc88cd13f82d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Applied Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Proscia</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, SQL</t>
+          <t>AI Engineer, RAG, Gemini, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e723074c4747c5d7</t>
+          <t>https://www.indeed.com/viewjob?jk=83b70b275411d893</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Automation Tester</t>
+          <t>Senior AI Applied Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Gemini, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c78af16e0a852a6</t>
+          <t>https://www.indeed.com/viewjob?jk=1d872de658f5583a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (L5)</t>
+          <t>Microsoft Azure Specialist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Exiger</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42c03602c2583f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=4d356d9379a1d876</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (L5)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Exiger</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, MySQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, Apache Airflow, CI/CD, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd96deb9d86f0b77</t>
+          <t>https://www.indeed.com/viewjob?jk=a709e6e770f53ae5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Junior Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jefferson Center for Mental Health</t>
+          <t>Radion Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wheat Ridge, CO, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ff8dcbb36e6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=478993b6b2b98818</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer, Inference (AI Data Engineering)</t>
+          <t>Strong Middle DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>Matoffo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, Python, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=666f2ebd7f91f325</t>
+          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Professional, Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Git, Snowflake, Databricks, Kafka, Python, SQL, R</t>
+          <t>RAG, BigQuery, CI/CD, Jenkins, BigQuery, Kafka, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=611c7f1add24eef6</t>
+          <t>https://www.indeed.com/viewjob?jk=57e51c321e5db28e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Synapse, CI/CD, Databricks, PySpark, Tableau, MicroStrategy, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,112 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4bfa59e40a5e45</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Claude AI Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1295b90fb790979e</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Kubernetes Platform Administrator</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>MKS2 Technologies</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7acfe2de3765c880</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AI Engineer/Banking Domain</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, Hugging Face, TensorFlow, PyTorch, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8389d2351331bb64</t>
+          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-19.xlsx
+++ b/daily_matches/job_matches_2026-08-19.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>Platform Engineer VI Data Services</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, BigQuery</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Data Lake, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed75a25bf648004</t>
+          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Oteemo, Inc</t>
+          <t>Eurofins</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Stafford, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.4</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>Machine Learning Engineer, RAG, Azure ML, Azure ML Studio, Data Lake, MLflow, Apache Airflow, Git, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7510a53669a6bd9e</t>
+          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Network Automation Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ICONICS</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c07ff9f974ddcb</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6a236d435cfe02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Matoffo</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, Apache Airflow, CI/CD</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9135a734bc453bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9e27255ec7a1ce</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Senior Platform &amp; SRE Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Kinesis, CI/CD, Terraform, Git, Snowflake, Databricks, Redshift, Kafka</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2118e94d973400</t>
+          <t>https://www.indeed.com/viewjob?jk=da2e41bf292dd62a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Generative AI Engineer / QA Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>World Emblem International</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, CI/CD, Snowflake, BigQuery, Hadoop</t>
+          <t>AI Engineer, LangChain, RAG, S3, Kubernetes, AKS, Terraform, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ed1844d162074</t>
+          <t>https://www.indeed.com/viewjob?jk=619b1ae49dfe1154</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Software Engineer II - Java, AI - ​Amex Offers &amp; Digital Media</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+          <t>Data Scientist, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69ff9ff69aac8b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a383e3eb1b6854f7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, BigQuery, Python</t>
+          <t>AI Engineer, RAG, PyTorch, Azure ML, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4134fc88cd13f82d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a97964923f244ff</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Applied Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, RAG, PyTorch, Azure ML, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83b70b275411d893</t>
+          <t>https://www.indeed.com/viewjob?jk=33d7d7c7d8354977</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Applied Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, RAG, PyTorch, Azure ML, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d872de658f5583a</t>
+          <t>https://www.indeed.com/viewjob?jk=aea0b8f4a9d48f00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, RAG, PyTorch, Azure ML, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d356d9379a1d876</t>
+          <t>https://www.indeed.com/viewjob?jk=3f2ee614624fd428</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Software Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, Apache Airflow, CI/CD, BigQuery, Python, SQL, R</t>
+          <t>Dataflow, Kubernetes, Terraform, Kafka, Hadoop, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a709e6e770f53ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Junior Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Radion Health</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, LightGBM, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Glue, Redshift, Kubernetes, CI/CD, Databricks, Redshift, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=478993b6b2b98818</t>
+          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Strong Middle DevOps Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Matoffo</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, PySpark, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de948ee2b61b61a</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc7b2e2fd6ca121</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Professional, Software Engineer</t>
+          <t>Senior Data Scientist (Auto Loan Pricing)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Jenkins, BigQuery, Kafka, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Databricks, Hadoop, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e51c321e5db28e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f2717d898c43f6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Enterprise Data Warehouse</t>
+          <t>Data Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Mill</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>San Bruno, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Synapse, CI/CD, Databricks, PySpark, Tableau, MicroStrategy, SQL, R, Scala</t>
+          <t>CI/CD, Terraform, Snowflake, PostgreSQL, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a690f45591735710</t>
+          <t>https://www.indeed.com/viewjob?jk=3e71cb68a464c4dc</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-19.xlsx
+++ b/daily_matches/job_matches_2026-08-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Platform Engineer VI Data Services</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Data Lake, FastAPI, Docker, CI/CD</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95d2b8bcef6e6443</t>
+          <t>https://www.indeed.com/viewjob?jk=da8857ac7498424c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Head, AI Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Eurofins</t>
+          <t>Success Academy Charter Schools</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Stafford, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Azure ML, Azure ML Studio, Data Lake, MLflow, Apache Airflow, Git, PostgreSQL, NoSQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555375438c1e8b98</t>
+          <t>https://www.indeed.com/viewjob?jk=2bec1fa0a461f110</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Network Automation Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6a236d435cfe02</t>
+          <t>https://www.indeed.com/viewjob?jk=81c4062ee8a8164c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Software Engineer, Konnect Admin/Billing</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python</t>
+          <t>Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, Kafka, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9e27255ec7a1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=5616973f627d78f6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; SRE Engineer</t>
+          <t>Software Developer Sr</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2e41bf292dd62a</t>
+          <t>https://www.indeed.com/viewjob?jk=94de36f5c17a6db4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>World Emblem International</t>
+          <t>AI Fire</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, S3, Kubernetes, AKS, Terraform, PostgreSQL, Python, SQL</t>
+          <t>Glue, Athena, Redshift, Synapse, Data Lake, CI/CD, Databricks, Redshift, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619b1ae49dfe1154</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9844392ec8b665</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Full-Stack SaaS Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Church Online, LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, S3, Docker, CI/CD, Terraform, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a383e3eb1b6854f7</t>
+          <t>https://www.indeed.com/viewjob?jk=92bd3b1d025be8a0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Advanced Analyst II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Meijer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, PyTorch, Azure ML, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, NLTK, Azure ML, Synapse, Git, Databricks, PySpark, Power BI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a97964923f244ff</t>
+          <t>https://www.indeed.com/viewjob?jk=1bdee7b0ad85c7d6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Applied Machine Learning Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, PyTorch, Azure ML, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, BigQuery, Git, BigQuery, Python, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d7d7c7d8354977</t>
+          <t>https://www.indeed.com/viewjob?jk=e044f5951d3a0aa1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Applied Machine Learning Scientist 2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, PyTorch, Azure ML, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, BigQuery, Git, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aea0b8f4a9d48f00</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6e23a20de952db</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>C-BRAIN Data Engineer (Remote) - Neurology</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Washington University in St. Louis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, PyTorch, Azure ML, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Generative AI, RAG, Synapse, Data Lake, Apache Airflow, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f2ee614624fd428</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6e7926c1d2e476</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer III</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aplazo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dataflow, Kubernetes, Terraform, Kafka, Hadoop, MySQL, MongoDB, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7380fc50156c508</t>
+          <t>https://www.indeed.com/viewjob?jk=6f265c3932f589bf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>QA Automation Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Glue, Redshift, Kubernetes, CI/CD, Databricks, Redshift, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd423be7263fd117</t>
+          <t>https://www.indeed.com/viewjob?jk=f4cbbd6df10ad612</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer- Data Insights</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, PySpark, Python, SQL, R, Optimization</t>
+          <t>RAG, CI/CD, Git, Snowflake, Tableau, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc7b2e2fd6ca121</t>
+          <t>https://www.indeed.com/viewjob?jk=f46255dc80a86a4a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Scientist (Auto Loan Pricing)</t>
+          <t>Senior Machine Learning Engineer, AI Evaluation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Society for Human Resource Management (SHRM)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Databricks, Hadoop, Python, SQL, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, BigQuery, Git, BigQuery, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,42 +986,567 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f2717d898c43f6</t>
+          <t>https://www.indeed.com/viewjob?jk=3190eb53e7e9d394</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Platform</t>
+          <t>2027 Data &amp; AI Program - Summer Internship - Analyst - United States</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mill</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Bruno, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=defd74142b248b91</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Jenkins, Terraform, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ee8aa25169c3ff0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Alameda, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, Git, Kafka, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=308aeb93cece3d47</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Marketing</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>oura</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1805aa456bc5d860</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Forward Deployment Engineer - Remote (Travel to Boston, MA as required)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Syncreon Consulting</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>CI/CD, Terraform, Snowflake, PostgreSQL, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e71cb68a464c4dc</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26ad1cd498a7ba52</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, CI/CD, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=668818422c4692eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Forum Energy Technologies</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, CI/CD, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80b04f8c34adf32c</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Kafka, Hadoop, MongoDB, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d65d9fe891b3d937</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior ETL Developer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ocean Blue Solutions</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Databricks, PostgreSQL, Power BI, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6eb300f7d6bc4524</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Application Security Engineer IV</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92658d4e06ae2705</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CMAS-Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Terraform, Git, PostgreSQL, MongoDB, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ccec090154a81bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer / Data Scientist – Python &amp; GenAI</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>I8IS INC.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PySpark, Hadoop, MySQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dd0127e98e6029d</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sr Data Analyst</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Guild Mortgage Company LLC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, MySQL, MongoDB, Cassandra, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9f15ed27b86ceb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SAP Data Analytics (AI/ML)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Raritan, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fb3aa3f2083c27f</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sunbelt Rentals</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, MLflow, Databricks, Python, SQL, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79039807a5c69379</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Solution Engineer – West</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Coralogix</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb26636c23aa24a6</t>
         </is>
       </c>
     </row>
